--- a/poker/resources/sample/PrivilegeCard.xlsx
+++ b/poker/resources/sample/PrivilegeCard.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\A-work\config_SimMgmtVert1.0\游戏配置表\activity\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="PrivilegeCard" sheetId="1" r:id="rId1"/>
@@ -203,10 +208,10 @@
     <t>月卡</t>
   </si>
   <si>
-    <t>1990000_1069200</t>
-  </si>
-  <si>
-    <t>1990000_35600</t>
+    <t>1980000_15000</t>
+  </si>
+  <si>
+    <t>1980000_500</t>
   </si>
   <si>
     <t>1_google99|2_ios99</t>
@@ -215,10 +220,10 @@
     <t>季卡</t>
   </si>
   <si>
-    <t>1990000_6736500</t>
-  </si>
-  <si>
-    <t>1990000_74900</t>
+    <t>1980000_72000</t>
+  </si>
+  <si>
+    <t>1980000_800</t>
   </si>
   <si>
     <t>1_google499|2_ios499</t>
@@ -227,10 +232,10 @@
     <t>永久卡</t>
   </si>
   <si>
-    <t>1990000_38980500</t>
-  </si>
-  <si>
-    <t>1990000_216600</t>
+    <t>1980000_438000</t>
+  </si>
+  <si>
+    <t>1980000_1200</t>
   </si>
   <si>
     <t>1031350_1</t>
@@ -271,7 +276,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0" tint="-0.249977111117893"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1275,7 +1279,7 @@
     <col min="4" max="4" width="7.375" style="1" customWidth="1"/>
     <col min="5" max="5" width="8.875" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="18.875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="24.375" style="1" customWidth="1"/>
     <col min="8" max="8" width="20" style="1" customWidth="1"/>
     <col min="9" max="9" width="23.625" style="1" customWidth="1"/>
     <col min="10" max="10" width="25.75" style="1" customWidth="1"/>
@@ -1418,6 +1422,10 @@
       <c r="J5" s="1" t="s">
         <v>26</v>
       </c>
+      <c r="K5" s="1">
+        <f>500*30</f>
+        <v>15000</v>
+      </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1">
@@ -1447,6 +1455,10 @@
       <c r="J6" s="1" t="s">
         <v>30</v>
       </c>
+      <c r="K6" s="1">
+        <f>800*90</f>
+        <v>72000</v>
+      </c>
       <c r="L6"/>
       <c r="M6"/>
     </row>
@@ -1480,6 +1492,10 @@
       </c>
       <c r="J7" s="1" t="s">
         <v>35</v>
+      </c>
+      <c r="K7" s="1">
+        <f>1200*365</f>
+        <v>438000</v>
       </c>
       <c r="L7"/>
       <c r="M7"/>

--- a/poker/resources/sample/PrivilegeCard.xlsx
+++ b/poker/resources/sample/PrivilegeCard.xlsx
@@ -106,7 +106,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0">
+    <comment ref="K1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -134,7 +134,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="38">
   <si>
     <t>序列ID</t>
   </si>
@@ -163,6 +163,9 @@
     <t>额外道具</t>
   </si>
   <si>
+    <t>赠送倍率</t>
+  </si>
+  <si>
     <t>渠道商品ID</t>
   </si>
   <si>
@@ -200,6 +203,9 @@
   </si>
   <si>
     <t>getItem</t>
+  </si>
+  <si>
+    <t>multiples</t>
   </si>
   <si>
     <t>channelCommodity</t>
@@ -1270,7 +1276,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.625" style="1" customWidth="1"/>
@@ -1281,17 +1287,18 @@
     <col min="6" max="6" width="14.375" style="1" customWidth="1"/>
     <col min="7" max="7" width="24.375" style="1" customWidth="1"/>
     <col min="8" max="8" width="20" style="1" customWidth="1"/>
-    <col min="9" max="9" width="23.625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="25.75" style="1" customWidth="1"/>
-    <col min="11" max="11" width="9" style="1"/>
-    <col min="12" max="12" width="7.875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="26.75" style="1" customWidth="1"/>
-    <col min="14" max="14" width="9" style="1"/>
-    <col min="15" max="15" width="26.75" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="1"/>
+    <col min="9" max="9" width="17.125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="9.75" style="1" customWidth="1"/>
+    <col min="11" max="11" width="25.75" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9" style="1"/>
+    <col min="13" max="13" width="7.875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="26.75" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9" style="1"/>
+    <col min="16" max="16" width="26.75" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1319,71 +1326,80 @@
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="J3" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="J3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1393,8 +1409,9 @@
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -1402,7 +1419,7 @@
         <v>56001</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -1414,20 +1431,23 @@
         <v>0.99</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="K5" s="1">
+        <v>27</v>
+      </c>
+      <c r="J5" s="1">
+        <v>30</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L5" s="1">
         <f>500*30</f>
         <v>15000</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:14">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -1435,7 +1455,7 @@
         <v>56002</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D6" s="1">
         <v>2</v>
@@ -1447,22 +1467,25 @@
         <v>4.99</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K6" s="1">
+        <v>31</v>
+      </c>
+      <c r="J6" s="1">
+        <v>90</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" s="1">
         <f>800*90</f>
         <v>72000</v>
       </c>
-      <c r="L6"/>
       <c r="M6"/>
-    </row>
-    <row r="7" spans="1:13">
+      <c r="N6"/>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -1470,7 +1493,7 @@
         <v>56003</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -1482,91 +1505,94 @@
         <v>19.99</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="K7" s="1">
+        <v>36</v>
+      </c>
+      <c r="J7" s="1">
+        <v>999</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L7" s="1">
         <f>1200*365</f>
         <v>438000</v>
       </c>
-      <c r="L7"/>
       <c r="M7"/>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="L8"/>
+      <c r="N7"/>
+    </row>
+    <row r="8" spans="1:14">
       <c r="M8"/>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="L9"/>
+      <c r="N8"/>
+    </row>
+    <row r="9" spans="1:14">
       <c r="M9"/>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="L10"/>
+      <c r="N9"/>
+    </row>
+    <row r="10" spans="1:14">
       <c r="M10"/>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="L11"/>
+      <c r="N10"/>
+    </row>
+    <row r="11" spans="1:14">
       <c r="M11"/>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="L12"/>
+      <c r="N11"/>
+    </row>
+    <row r="12" spans="1:14">
       <c r="M12"/>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="L13"/>
+      <c r="N12"/>
+    </row>
+    <row r="13" spans="1:14">
       <c r="M13"/>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="L14"/>
+      <c r="N13"/>
+    </row>
+    <row r="14" spans="1:14">
       <c r="M14"/>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="L15"/>
+      <c r="N14"/>
+    </row>
+    <row r="15" spans="1:14">
       <c r="M15"/>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="L16"/>
+      <c r="N15"/>
+    </row>
+    <row r="16" spans="1:14">
       <c r="M16"/>
-    </row>
-    <row r="17" spans="12:13">
-      <c r="L17"/>
+      <c r="N16"/>
+    </row>
+    <row r="17" spans="13:14">
       <c r="M17"/>
-    </row>
-    <row r="18" spans="12:13">
-      <c r="L18"/>
+      <c r="N17"/>
+    </row>
+    <row r="18" spans="13:14">
       <c r="M18"/>
-    </row>
-    <row r="19" spans="12:13">
-      <c r="L19"/>
+      <c r="N18"/>
+    </row>
+    <row r="19" spans="13:14">
       <c r="M19"/>
-    </row>
-    <row r="20" spans="12:13">
-      <c r="L20"/>
+      <c r="N19"/>
+    </row>
+    <row r="20" spans="13:14">
       <c r="M20"/>
-    </row>
-    <row r="21" spans="12:13">
-      <c r="L21"/>
+      <c r="N20"/>
+    </row>
+    <row r="21" spans="13:14">
       <c r="M21"/>
-    </row>
-    <row r="22" spans="12:13">
-      <c r="L22"/>
+      <c r="N21"/>
+    </row>
+    <row r="22" spans="13:14">
       <c r="M22"/>
-    </row>
-    <row r="23" spans="12:13">
-      <c r="L23"/>
+      <c r="N22"/>
+    </row>
+    <row r="23" spans="13:14">
       <c r="M23"/>
-    </row>
-    <row r="24" spans="12:13">
-      <c r="L24"/>
+      <c r="N23"/>
+    </row>
+    <row r="24" spans="13:14">
       <c r="M24"/>
+      <c r="N24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
